--- a/simulation_data/tuesday_evening.xlsx
+++ b/simulation_data/tuesday_evening.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>system_time_min</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>service_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,11 @@
       <c r="G2" t="n">
         <v>1.66717678486399</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
       <c r="G3" t="n">
         <v>0.7559276133160773</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +566,11 @@
       <c r="G4" t="n">
         <v>2.031065598357719</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +600,11 @@
       <c r="G5" t="n">
         <v>2.236349721807443</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +634,11 @@
       <c r="G6" t="n">
         <v>2.706506973771185</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +668,11 @@
       <c r="G7" t="n">
         <v>1.967467151068554</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +702,11 @@
       <c r="G8" t="n">
         <v>1.04579922251804</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +736,11 @@
       <c r="G9" t="n">
         <v>2.516438101991686</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +770,11 @@
       <c r="G10" t="n">
         <v>2.208253603684264</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +804,11 @@
       <c r="G11" t="n">
         <v>3.037520372025657</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +838,11 @@
       <c r="G12" t="n">
         <v>3.100932742618384</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +872,11 @@
       <c r="G13" t="n">
         <v>2.904729613685527</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +906,11 @@
       <c r="G14" t="n">
         <v>3.151038176367237</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +940,11 @@
       <c r="G15" t="n">
         <v>3.123553123230191</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,6 +974,11 @@
       <c r="G16" t="n">
         <v>2.340627344120426</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +1008,11 @@
       <c r="G17" t="n">
         <v>0.6840778376389032</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,6 +1042,11 @@
       <c r="G18" t="n">
         <v>3.724930712104539</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,6 +1076,11 @@
       <c r="G19" t="n">
         <v>4.229996650631353</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1015,6 +1110,11 @@
       <c r="G20" t="n">
         <v>3.795449740028154</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1044,6 +1144,11 @@
       <c r="G21" t="n">
         <v>3.559596920259366</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1073,6 +1178,11 @@
       <c r="G22" t="n">
         <v>2.315239244680496</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1102,6 +1212,11 @@
       <c r="G23" t="n">
         <v>2.277688039199331</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1246,11 @@
       <c r="G24" t="n">
         <v>1.966130067247345</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1160,6 +1280,11 @@
       <c r="G25" t="n">
         <v>2.131715016599766</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1314,11 @@
       <c r="G26" t="n">
         <v>0.8184506741477952</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1218,6 +1348,11 @@
       <c r="G27" t="n">
         <v>2.516972342617023</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1247,6 +1382,11 @@
       <c r="G28" t="n">
         <v>1.375962602322384</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1276,6 +1416,11 @@
       <c r="G29" t="n">
         <v>2.332177796069403</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,6 +1450,11 @@
       <c r="G30" t="n">
         <v>6.543275029812571</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1334,6 +1484,11 @@
       <c r="G31" t="n">
         <v>4.818108747430826</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1363,6 +1518,11 @@
       <c r="G32" t="n">
         <v>0.9814681205711153</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1392,6 +1552,11 @@
       <c r="G33" t="n">
         <v>2.684408675367064</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,6 +1586,11 @@
       <c r="G34" t="n">
         <v>2.833676824734586</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1450,6 +1620,11 @@
       <c r="G35" t="n">
         <v>2.010950689288309</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1479,6 +1654,11 @@
       <c r="G36" t="n">
         <v>4.61558577892912</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1508,6 +1688,11 @@
       <c r="G37" t="n">
         <v>3.580699251528789</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1537,6 +1722,11 @@
       <c r="G38" t="n">
         <v>2.616438493927451</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1566,6 +1756,11 @@
       <c r="G39" t="n">
         <v>3.076623864570798</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1595,6 +1790,11 @@
       <c r="G40" t="n">
         <v>5.641052753846114</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1624,6 +1824,11 @@
       <c r="G41" t="n">
         <v>4.617552824689776</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1653,6 +1858,11 @@
       <c r="G42" t="n">
         <v>4.989822299113753</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1682,6 +1892,11 @@
       <c r="G43" t="n">
         <v>4.484515161915946</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1711,6 +1926,11 @@
       <c r="G44" t="n">
         <v>3.396033042844927</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1740,6 +1960,11 @@
       <c r="G45" t="n">
         <v>3.180424479664117</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1769,6 +1994,11 @@
       <c r="G46" t="n">
         <v>6.53815256874922</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1798,6 +2028,11 @@
       <c r="G47" t="n">
         <v>2.701229012591798</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,6 +2062,11 @@
       <c r="G48" t="n">
         <v>3.331103733177843</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1856,6 +2096,11 @@
       <c r="G49" t="n">
         <v>3.919270676883383</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1885,6 +2130,11 @@
       <c r="G50" t="n">
         <v>1.730338946497217</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1914,6 +2164,11 @@
       <c r="G51" t="n">
         <v>2.131442836081714</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1943,6 +2198,11 @@
       <c r="G52" t="n">
         <v>3.771927632043555</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1972,6 +2232,11 @@
       <c r="G53" t="n">
         <v>2.072371443275655</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,6 +2266,11 @@
       <c r="G54" t="n">
         <v>3.132842237522614</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2030,6 +2300,11 @@
       <c r="G55" t="n">
         <v>3.51290222462713</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2059,6 +2334,11 @@
       <c r="G56" t="n">
         <v>3.642779629462706</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2088,6 +2368,11 @@
       <c r="G57" t="n">
         <v>2.663962381283683</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2117,6 +2402,11 @@
       <c r="G58" t="n">
         <v>2.46900782707014</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2145,6 +2435,11 @@
       </c>
       <c r="G59" t="n">
         <v>0.9841818355601724</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
       </c>
     </row>
   </sheetData>
